--- a/survey_templates/038_online_gaming_platform_overview--survey_templates.xlsx
+++ b/survey_templates/038_online_gaming_platform_overview--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -838,8 +838,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'very_satisfied'}</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_satisfied'}</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'not_satisfied'}</t>
+          <t>not satisfied</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'very_dissatisfied'}</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all_satisfied'}</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'not_at_all_satisfied'}</t>
+          <t>not at all satisfied</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'action'}</t>
+          <t>action</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'action'}</t>
+          <t>action</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'adventure'}</t>
+          <t>adventure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'adventure'}</t>
+          <t>adventure</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'role-playing'}</t>
+          <t>role-playing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'role-playing'}</t>
+          <t>role-playing</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'sports'}</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'sports'}</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'puzzle'}</t>
+          <t>puzzle</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'puzzle'}</t>
+          <t>puzzle</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'simulation'}</t>
+          <t>simulation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'simulation'}</t>
+          <t>simulation</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'xbox'}</t>
+          <t>xbox</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Xbox'}</t>
+          <t>Xbox</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'playstation'}</t>
+          <t>playstation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'PlayStation'}</t>
+          <t>PlayStation</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'nintendo'}</t>
+          <t>nintendo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Nintendo'}</t>
+          <t>Nintendo</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'pc'}</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'PC'}</t>
+          <t>PC</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Mobile'}</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'switch'}</t>
+          <t>switch</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Switch'}</t>
+          <t>Switch</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'browser'}</t>
+          <t>browser</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'browser'}</t>
+          <t>browser</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'very_good'}</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_good'}</t>
+          <t>somewhat_good</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_good'}</t>
+          <t>somewhat good</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_bad'}</t>
+          <t>somewhat_bad</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_bad'}</t>
+          <t>somewhat bad</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'very_bad'}</t>
+          <t>very bad</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'action'}</t>
+          <t>action</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'action'}</t>
+          <t>action</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'adventure'}</t>
+          <t>adventure</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'adventure'}</t>
+          <t>adventure</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'role-playing'}</t>
+          <t>role-playing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'role-playing'}</t>
+          <t>role-playing</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'sports'}</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'sports'}</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'puzzle'}</t>
+          <t>puzzle</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'puzzle'}</t>
+          <t>puzzle</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'simulation'}</t>
+          <t>simulation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'simulation'}</t>
+          <t>simulation</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'xbox'}</t>
+          <t>xbox</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Xbox'}</t>
+          <t>Xbox</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'playstation'}</t>
+          <t>playstation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'PlayStation'}</t>
+          <t>PlayStation</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'nintendo'}</t>
+          <t>nintendo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Nintendo'}</t>
+          <t>Nintendo</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'pc'}</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'PC'}</t>
+          <t>PC</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'Mobile'}</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'switch'}</t>
+          <t>switch</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'Switch'}</t>
+          <t>Switch</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
